--- a/Datos_oficioremision.xlsx
+++ b/Datos_oficioremision.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manuel\Desktop\uca\5\SIE\proyectorepo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manuel\Desktop\uca\5\SIE\proyectorepo\SIE-Grupo-APPLE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478CFD1E-B1AE-4617-B6C6-E04A7AFCD53B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3BB1E1F-8193-45CB-B9E7-D49CB9ED94E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{89460A5D-6D94-44C2-BF87-60F6987698AF}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="101">
   <si>
     <t>Municipio</t>
   </si>
@@ -211,9 +211,6 @@
     <t>Mancomunidad del Campo de Gibraltar</t>
   </si>
   <si>
-    <t>Mancounidad de la sierra de Cádiz</t>
-  </si>
-  <si>
     <t>Zahara de los Atunes</t>
   </si>
   <si>
@@ -332,6 +329,18 @@
   </si>
   <si>
     <t>D. Carlos García Rodríguez</t>
+  </si>
+  <si>
+    <t>Atributo</t>
+  </si>
+  <si>
+    <t>Mancomunidad</t>
+  </si>
+  <si>
+    <t>ELA</t>
+  </si>
+  <si>
+    <t>Mancomunidad de la sierra de Cádiz</t>
   </si>
 </sst>
 </file>
@@ -385,17 +394,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -732,491 +739,551 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3606FAFD-1884-47F2-8486-B1950726AF05}">
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="4"/>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="4"/>
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="4"/>
+      <c r="B4" t="s">
+        <v>0</v>
+      </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="4"/>
+      <c r="B5" t="s">
+        <v>0</v>
+      </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="4"/>
+      <c r="B6" t="s">
+        <v>0</v>
+      </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="4"/>
+      <c r="B7" t="s">
+        <v>0</v>
+      </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="4"/>
+      <c r="B8" t="s">
+        <v>0</v>
+      </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="4"/>
+      <c r="B9" t="s">
+        <v>0</v>
+      </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="4"/>
+      <c r="B10" t="s">
+        <v>0</v>
+      </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="4"/>
+      <c r="B11" t="s">
+        <v>0</v>
+      </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="4"/>
+      <c r="B12" t="s">
+        <v>0</v>
+      </c>
       <c r="C12" s="2"/>
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="4"/>
+      <c r="B13" t="s">
+        <v>0</v>
+      </c>
       <c r="C13" s="2"/>
-      <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="4"/>
+      <c r="B14" t="s">
+        <v>0</v>
+      </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="4"/>
+      <c r="B15" t="s">
+        <v>0</v>
+      </c>
       <c r="C15" s="2"/>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="4"/>
+      <c r="B16" t="s">
+        <v>0</v>
+      </c>
       <c r="C16" s="2"/>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="4"/>
+      <c r="B17" t="s">
+        <v>0</v>
+      </c>
       <c r="C17" s="2"/>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="4"/>
+      <c r="B18" t="s">
+        <v>0</v>
+      </c>
       <c r="C18" s="2"/>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="4"/>
+      <c r="B19" t="s">
+        <v>0</v>
+      </c>
       <c r="C19" s="2"/>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="4"/>
+      <c r="B20" t="s">
+        <v>0</v>
+      </c>
       <c r="C20" s="2"/>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="4"/>
+      <c r="B21" t="s">
+        <v>0</v>
+      </c>
       <c r="C21" s="2"/>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="4"/>
+      <c r="B22" t="s">
+        <v>0</v>
+      </c>
       <c r="C22" s="2"/>
-      <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="4"/>
+      <c r="B23" t="s">
+        <v>0</v>
+      </c>
       <c r="C23" s="2"/>
-      <c r="D23" s="3"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="4"/>
+      <c r="B24" t="s">
+        <v>0</v>
+      </c>
       <c r="C24" s="2"/>
-      <c r="D24" s="3"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>47</v>
       </c>
-      <c r="B25" s="4"/>
+      <c r="B25" t="s">
+        <v>0</v>
+      </c>
       <c r="C25" s="2"/>
-      <c r="D25" s="3"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="4"/>
+      <c r="B26" t="s">
+        <v>0</v>
+      </c>
       <c r="C26" s="2"/>
-      <c r="D26" s="3"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="4"/>
+      <c r="B27" t="s">
+        <v>0</v>
+      </c>
       <c r="C27" s="2"/>
-      <c r="D27" s="3"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>13</v>
       </c>
-      <c r="B28" s="4"/>
+      <c r="B28" t="s">
+        <v>0</v>
+      </c>
       <c r="C28" s="2"/>
-      <c r="D28" s="3"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>15</v>
       </c>
-      <c r="B29" s="4"/>
+      <c r="B29" t="s">
+        <v>0</v>
+      </c>
       <c r="C29" s="2"/>
-      <c r="D29" s="3"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>48</v>
       </c>
-      <c r="B30" s="4"/>
+      <c r="B30" t="s">
+        <v>0</v>
+      </c>
       <c r="C30" s="2"/>
-      <c r="D30" s="3"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>17</v>
       </c>
-      <c r="B31" s="4"/>
+      <c r="B31" t="s">
+        <v>0</v>
+      </c>
       <c r="C31" s="2"/>
-      <c r="D31" s="3"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>49</v>
       </c>
-      <c r="B32" s="4"/>
+      <c r="B32" t="s">
+        <v>0</v>
+      </c>
       <c r="C32" s="2"/>
-      <c r="D32" s="3"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>50</v>
       </c>
-      <c r="B33" s="4"/>
+      <c r="B33" t="s">
+        <v>0</v>
+      </c>
       <c r="C33" s="2"/>
-      <c r="D33" s="3"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>10</v>
       </c>
-      <c r="B34" s="4"/>
+      <c r="B34" t="s">
+        <v>0</v>
+      </c>
       <c r="C34" s="2"/>
-      <c r="D34" s="3"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>51</v>
       </c>
-      <c r="B35" s="4"/>
+      <c r="B35" t="s">
+        <v>0</v>
+      </c>
       <c r="C35" s="2"/>
-      <c r="D35" s="3"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>52</v>
       </c>
-      <c r="B36" s="4"/>
+      <c r="B36" t="s">
+        <v>0</v>
+      </c>
       <c r="C36" s="2"/>
-      <c r="D36" s="3"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>6</v>
       </c>
-      <c r="B37" s="4"/>
+      <c r="B37" t="s">
+        <v>0</v>
+      </c>
       <c r="C37" s="2"/>
-      <c r="D37" s="3"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>26</v>
       </c>
-      <c r="B38" s="4"/>
+      <c r="B38" t="s">
+        <v>0</v>
+      </c>
       <c r="C38" s="2"/>
-      <c r="D38" s="3"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>3</v>
       </c>
-      <c r="B39" s="4"/>
+      <c r="B39" t="s">
+        <v>0</v>
+      </c>
       <c r="C39" s="2"/>
-      <c r="D39" s="3"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>18</v>
       </c>
-      <c r="B40" s="4"/>
+      <c r="B40" t="s">
+        <v>0</v>
+      </c>
       <c r="C40" s="2"/>
-      <c r="D40" s="3"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>25</v>
       </c>
-      <c r="B41" s="4"/>
+      <c r="B41" t="s">
+        <v>0</v>
+      </c>
       <c r="C41" s="2"/>
-      <c r="D41" s="3"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>24</v>
       </c>
-      <c r="B42" s="4"/>
+      <c r="B42" t="s">
+        <v>0</v>
+      </c>
       <c r="C42" s="2"/>
-      <c r="D42" s="3"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>1</v>
       </c>
-      <c r="B43" s="4"/>
+      <c r="B43" t="s">
+        <v>0</v>
+      </c>
       <c r="C43" s="2"/>
-      <c r="D43" s="3"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>23</v>
       </c>
-      <c r="B44" s="4"/>
+      <c r="B44" t="s">
+        <v>0</v>
+      </c>
       <c r="C44" s="2"/>
-      <c r="D44" s="3"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>53</v>
       </c>
-      <c r="B45" s="4"/>
+      <c r="B45" t="s">
+        <v>0</v>
+      </c>
       <c r="C45" s="2"/>
-      <c r="D45" s="3"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>54</v>
       </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="3"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
+      <c r="B46" t="s">
+        <v>98</v>
+      </c>
+      <c r="C46" s="3"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>55</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="3"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
+      <c r="B47" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" s="3"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>56</v>
       </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="3"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
+      <c r="B48" t="s">
+        <v>98</v>
+      </c>
+      <c r="C48" s="3"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>100</v>
+      </c>
+      <c r="B49" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49" s="3"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>57</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="3"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
+      <c r="B50" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" s="3"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>58</v>
       </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="3"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
+      <c r="B51" t="s">
+        <v>99</v>
+      </c>
+      <c r="C51" s="2"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>59</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="3"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
+      <c r="B52" t="s">
+        <v>99</v>
+      </c>
+      <c r="C52" s="3"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>60</v>
       </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="3"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
+      <c r="B53" t="s">
+        <v>99</v>
+      </c>
+      <c r="C53" s="3"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>61</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="3"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
+      <c r="B54" t="s">
+        <v>99</v>
+      </c>
+      <c r="C54" s="3"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>62</v>
       </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="3"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="4" t="s">
+      <c r="B55" t="s">
+        <v>99</v>
+      </c>
+      <c r="C55" s="3"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>63</v>
       </c>
-      <c r="B55" s="4"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="3"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="s">
+      <c r="B56" t="s">
+        <v>99</v>
+      </c>
+      <c r="C56" s="3"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>64</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="3"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="4" t="s">
+      <c r="B57" t="s">
+        <v>99</v>
+      </c>
+      <c r="C57" s="3"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>7</v>
+      </c>
+      <c r="B58" t="s">
+        <v>99</v>
+      </c>
+      <c r="C58" s="3"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>65</v>
       </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="3"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="3"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="4" t="s">
+      <c r="B59" t="s">
+        <v>99</v>
+      </c>
+      <c r="C59" s="3"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>66</v>
       </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="3"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B60" s="4"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="3"/>
+      <c r="B60" t="s">
+        <v>99</v>
+      </c>
+      <c r="C60" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1239,152 +1306,152 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_oficioremision.xlsx
+++ b/Datos_oficioremision.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manuel\Desktop\uca\5\SIE\proyectorepo\SIE-Grupo-APPLE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manue\Desktop\cosas-cosotas\5\SIE\SIE-Grupo-APPLE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3BB1E1F-8193-45CB-B9E7-D49CB9ED94E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF68C412-0B04-47A9-A356-229361D66D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{89460A5D-6D94-44C2-BF87-60F6987698AF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{89460A5D-6D94-44C2-BF87-60F6987698AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Municipios" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="103">
   <si>
     <t>Municipio</t>
   </si>
@@ -341,6 +341,12 @@
   </si>
   <si>
     <t>Mancomunidad de la sierra de Cádiz</t>
+  </si>
+  <si>
+    <t>ASESOR</t>
+  </si>
+  <si>
+    <t>COLABORADOR</t>
   </si>
 </sst>
 </file>
@@ -740,13 +746,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3606FAFD-1884-47F2-8486-B1950726AF05}">
   <dimension ref="A1:C60"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="1" max="1" width="36.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -754,7 +760,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -763,7 +769,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -772,7 +778,7 @@
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -781,7 +787,7 @@
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -790,7 +796,7 @@
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -799,7 +805,7 @@
       </c>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -808,7 +814,7 @@
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -817,7 +823,7 @@
       </c>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -826,7 +832,7 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -835,7 +841,7 @@
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -844,7 +850,7 @@
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>41</v>
       </c>
@@ -853,7 +859,7 @@
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -862,7 +868,7 @@
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -871,7 +877,7 @@
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -880,7 +886,7 @@
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -889,7 +895,7 @@
       </c>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -898,7 +904,7 @@
       </c>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -907,7 +913,7 @@
       </c>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -916,7 +922,7 @@
       </c>
       <c r="C19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -925,7 +931,7 @@
       </c>
       <c r="C20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -934,7 +940,7 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>45</v>
       </c>
@@ -943,7 +949,7 @@
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -952,7 +958,7 @@
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>46</v>
       </c>
@@ -961,7 +967,7 @@
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>47</v>
       </c>
@@ -970,7 +976,7 @@
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -979,7 +985,7 @@
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -988,7 +994,7 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>13</v>
       </c>
@@ -997,7 +1003,7 @@
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>15</v>
       </c>
@@ -1006,7 +1012,7 @@
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>48</v>
       </c>
@@ -1015,7 +1021,7 @@
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>17</v>
       </c>
@@ -1024,7 +1030,7 @@
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>49</v>
       </c>
@@ -1033,7 +1039,7 @@
       </c>
       <c r="C32" s="2"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>50</v>
       </c>
@@ -1042,7 +1048,7 @@
       </c>
       <c r="C33" s="2"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -1051,7 +1057,7 @@
       </c>
       <c r="C34" s="2"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>51</v>
       </c>
@@ -1060,7 +1066,7 @@
       </c>
       <c r="C35" s="2"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>52</v>
       </c>
@@ -1069,7 +1075,7 @@
       </c>
       <c r="C36" s="2"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -1078,7 +1084,7 @@
       </c>
       <c r="C37" s="2"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>26</v>
       </c>
@@ -1087,7 +1093,7 @@
       </c>
       <c r="C38" s="2"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>3</v>
       </c>
@@ -1096,7 +1102,7 @@
       </c>
       <c r="C39" s="2"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -1105,7 +1111,7 @@
       </c>
       <c r="C40" s="2"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>25</v>
       </c>
@@ -1114,7 +1120,7 @@
       </c>
       <c r="C41" s="2"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>24</v>
       </c>
@@ -1123,7 +1129,7 @@
       </c>
       <c r="C42" s="2"/>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>1</v>
       </c>
@@ -1132,7 +1138,7 @@
       </c>
       <c r="C43" s="2"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>23</v>
       </c>
@@ -1141,7 +1147,7 @@
       </c>
       <c r="C44" s="2"/>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>53</v>
       </c>
@@ -1150,7 +1156,7 @@
       </c>
       <c r="C45" s="2"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>54</v>
       </c>
@@ -1159,7 +1165,7 @@
       </c>
       <c r="C46" s="3"/>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>55</v>
       </c>
@@ -1168,7 +1174,7 @@
       </c>
       <c r="C47" s="3"/>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -1177,7 +1183,7 @@
       </c>
       <c r="C48" s="3"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>100</v>
       </c>
@@ -1186,7 +1192,7 @@
       </c>
       <c r="C49" s="3"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>57</v>
       </c>
@@ -1195,7 +1201,7 @@
       </c>
       <c r="C50" s="3"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>58</v>
       </c>
@@ -1204,7 +1210,7 @@
       </c>
       <c r="C51" s="2"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>59</v>
       </c>
@@ -1213,7 +1219,7 @@
       </c>
       <c r="C52" s="3"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>60</v>
       </c>
@@ -1222,7 +1228,7 @@
       </c>
       <c r="C53" s="3"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -1231,7 +1237,7 @@
       </c>
       <c r="C54" s="3"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -1240,7 +1246,7 @@
       </c>
       <c r="C55" s="3"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -1249,7 +1255,7 @@
       </c>
       <c r="C56" s="3"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -1258,7 +1264,7 @@
       </c>
       <c r="C57" s="3"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -1267,7 +1273,7 @@
       </c>
       <c r="C58" s="3"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>65</v>
       </c>
@@ -1276,7 +1282,7 @@
       </c>
       <c r="C59" s="3"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>66</v>
       </c>
@@ -1294,162 +1300,162 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{473D6359-92CE-479F-9B62-92C1E4CE4353}">
   <dimension ref="A1:A31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.7109375" customWidth="1"/>
+    <col min="1" max="1" width="29.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>96</v>
       </c>
@@ -1462,45 +1468,55 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{195EBCBB-C110-4D7C-9373-C6B300948B3C}">
-  <dimension ref="A1:A7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
